--- a/Misc/spider_marks.xlsx
+++ b/Misc/spider_marks.xlsx
@@ -133,11 +133,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="84689283"/>
-        <c:axId val="2023491941"/>
+        <c:axId val="1614496745"/>
+        <c:axId val="1162190925"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="84689283"/>
+        <c:axId val="1614496745"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -189,10 +189,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2023491941"/>
+        <c:crossAx val="1162190925"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2023491941"/>
+        <c:axId val="1162190925"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="6.0"/>
@@ -268,7 +268,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84689283"/>
+        <c:crossAx val="1614496745"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
